--- a/Predix Finance - FIIS.xlsx
+++ b/Predix Finance - FIIS.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 10\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25203163-7EA0-4DB5-B0BA-7DE5074F946B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7589ACA-57C9-4CE4-8541-93C952B72B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EF3548C7-D4D4-4023-9A0B-3FFFB342BF78}"/>
   </bookViews>
   <sheets>
     <sheet name="Predix" sheetId="1" r:id="rId1"/>
-    <sheet name="Configuracao _Perfil_Investidor" sheetId="2" r:id="rId2"/>
-    <sheet name="Grafico_Alocacao_dados" sheetId="3" r:id="rId3"/>
+    <sheet name="Configuracao _Perfil_Investidor" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Grafico_Alocacao_dados" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Aporte_mensal">Predix!$C$19</definedName>
@@ -316,7 +316,7 @@
       <name val="Poppins ExtraBold"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,19 +348,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,6 +361,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,7 +750,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -893,20 +887,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="24" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
@@ -928,76 +912,58 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="10" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1007,6 +973,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="24" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3488,7 +3485,7 @@
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="92">
         <v>7000</v>
       </c>
       <c r="E19" s="45" t="s">
@@ -3583,96 +3580,96 @@
     </row>
     <row r="24" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55" t="s">
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="95"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="59">
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="96">
         <f>Aporte_mensal</f>
         <v>7000</v>
       </c>
-      <c r="F26" s="59"/>
-      <c r="G26" s="60"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="56"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="61"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="60"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="56"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64" t="s">
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="64"/>
-      <c r="G28" s="65" t="s">
+      <c r="F28" s="60"/>
+      <c r="G28" s="61" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="66">
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="62">
         <f>VLOOKUP($E$25&amp;"-"&amp;B29,'Configuracao _Perfil_Investidor'!A3:D9,4,FALSE)</f>
         <v>0.8</v>
       </c>
-      <c r="F29" s="66"/>
-      <c r="G29" s="67">
+      <c r="F29" s="62"/>
+      <c r="G29" s="63">
         <f>$E$26*E29</f>
         <v>5600</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="66">
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="62">
         <f>VLOOKUP($E$25&amp;"-"&amp;B30,'Configuracao _Perfil_Investidor'!A4:D10,4,FALSE)</f>
         <v>0.2</v>
       </c>
-      <c r="F30" s="66"/>
-      <c r="G30" s="67">
+      <c r="F30" s="62"/>
+      <c r="G30" s="63">
         <f>$E$26*E30</f>
         <v>1400</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="95">
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="85">
         <f>SUM(E29:F30)</f>
         <v>1</v>
       </c>
-      <c r="F31" s="94"/>
-      <c r="G31" s="68">
+      <c r="F31" s="84"/>
+      <c r="G31" s="64">
         <f>SUM(G29:G30)</f>
         <v>7000</v>
       </c>
@@ -3682,48 +3679,48 @@
       <c r="A33" s="7">
         <v>2</v>
       </c>
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70" t="str">
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87" t="str">
         <f>$E$25</f>
         <v>Conservador</v>
       </c>
-      <c r="F33" s="70"/>
-      <c r="G33" s="71"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="88"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>5</v>
       </c>
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="74">
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="67">
         <v>1</v>
       </c>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="68"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>10</v>
       </c>
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="78">
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="71">
         <f>$G$30*$E$34</f>
         <v>1400</v>
       </c>
-      <c r="F35" s="78"/>
-      <c r="G35" s="79"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="72"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
@@ -3740,111 +3737,111 @@
       <c r="A37" s="7">
         <v>30</v>
       </c>
-      <c r="B37" s="80" t="s">
+      <c r="B37" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81" t="s">
+      <c r="C37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="81"/>
-      <c r="G37" s="82" t="s">
+      <c r="F37" s="90"/>
+      <c r="G37" s="91" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="89" t="s">
+      <c r="B38" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="84">
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="74">
         <f>VLOOKUP($E$25&amp;"-"&amp;B38,'Configuracao _Perfil_Investidor'!$F$4:$I$18,4,FALSE)</f>
         <v>0.3</v>
       </c>
-      <c r="F38" s="83"/>
-      <c r="G38" s="87">
+      <c r="F38" s="73"/>
+      <c r="G38" s="77">
         <f>$E$35*E38</f>
         <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="89" t="s">
+      <c r="B39" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="84">
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="74">
         <f>VLOOKUP($E$25&amp;"-"&amp;B39,'Configuracao _Perfil_Investidor'!$F$4:$I$18,4,FALSE)</f>
         <v>0.35</v>
       </c>
-      <c r="F39" s="83"/>
-      <c r="G39" s="87">
+      <c r="F39" s="73"/>
+      <c r="G39" s="77">
         <f>$E$35*E39</f>
         <v>489.99999999999994</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="89" t="s">
+      <c r="B40" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="90"/>
-      <c r="D40" s="90"/>
-      <c r="E40" s="84">
+      <c r="C40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="74">
         <f>VLOOKUP($E$25&amp;"-"&amp;B40,'Configuracao _Perfil_Investidor'!$F$4:$I$18,4,FALSE)</f>
         <v>0.2</v>
       </c>
-      <c r="F40" s="83"/>
-      <c r="G40" s="87">
+      <c r="F40" s="73"/>
+      <c r="G40" s="77">
         <f>$E$35*E40</f>
         <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="89" t="s">
+      <c r="B41" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="84">
+      <c r="C41" s="80"/>
+      <c r="D41" s="80"/>
+      <c r="E41" s="74">
         <f>VLOOKUP($E$25&amp;"-"&amp;B41,'Configuracao _Perfil_Investidor'!$F$4:$I$18,4,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="83"/>
-      <c r="G41" s="87">
+      <c r="F41" s="73"/>
+      <c r="G41" s="77">
         <f>$E$35*E41</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="89" t="s">
+      <c r="B42" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="90"/>
-      <c r="D42" s="90"/>
-      <c r="E42" s="84">
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="74">
         <f>VLOOKUP($E$25&amp;"-"&amp;B42,'Configuracao _Perfil_Investidor'!$F$4:$I$18,4,FALSE)</f>
         <v>0.15</v>
       </c>
-      <c r="F42" s="83"/>
-      <c r="G42" s="87">
+      <c r="F42" s="73"/>
+      <c r="G42" s="77">
         <f>$E$35*E42</f>
         <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="91" t="s">
+      <c r="B43" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="92"/>
-      <c r="D43" s="92"/>
-      <c r="E43" s="86">
+      <c r="C43" s="82"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="76">
         <f>SUM(E38:E42)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F43" s="85"/>
-      <c r="G43" s="88">
+      <c r="F43" s="75"/>
+      <c r="G43" s="78">
         <f>SUM(G38:G42)</f>
         <v>1400</v>
       </c>
